--- a/processo_2/outputs/estatisticas_enquadramento.xlsx
+++ b/processo_2/outputs/estatisticas_enquadramento.xlsx
@@ -414,15 +414,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,20 +442,40 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Área de Conhecimento</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Coordenador</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Título do Projeto</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Status Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ODS Vinculado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Inovação Tecnológica</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Gera Patente</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Qtd Inconformidades</t>
         </is>
@@ -460,37 +484,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PROPOSTA_007</t>
+          <t>PROPOSTA_004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FAENG</t>
+          <t>FAODO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Juliana Prado</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Projeto de Fonte de Alimentação Linear 12V e 5V - Estudo de Caso 007</t>
+          <t>Aline Bezerra Soares</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Reconhecimento de Padrões em Sinais Biomédicos - Estudo de Caso 004</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>NÃO ENQUADRADA</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ODS 7</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PROPOSTA_039</t>
+          <t>PROPOSTA_003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -500,111 +544,141 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Juliana Prado</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aplicações de Computação Quântica em Otimização - Estudo de Caso 039</t>
+          <t>Eduardo Henrique Lima</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Plataforma de Ensino Adaptativo com IA - Estudo de Caso 003</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>NÃO ENQUADRADA</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ODS 9</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PROPOSTA_025</t>
+          <t>PROPOSTA_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAENG</t>
+          <t>FACOM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Juliana Prado</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Internet das Coisas aplicada à Pecuária - Estudo de Caso 025</t>
+          <t>Ana Lopes da Silva</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Modelagem de Sistemas Multiagentes - Estudo de Caso 001</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>NÃO ENQUADRADA</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>2</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ODS 9</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROPOSTA_001</t>
+          <t>PROPOSTA_002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FAENG</t>
+          <t>FACOM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Juliana Prado</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Desenvolvimento de Jogos Educacionais Interativos - Estudo de Caso 001</t>
+          <t>Bruno Pereira Pontes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Aplicação de Redes Neurais em Reconhecimento Facial - Estudo de Caso 002</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>NÃO ENQUADRADA</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ODS 2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PROPOSTA_040</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>INISA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Matheus Augusto Cintra</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mineração de Dados em Ambientes Educacionais - Estudo de Caso 040</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NÃO ENQUADRADA</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,23 +719,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Limite de Propostas</t>
+          <t>Verificação de Titulação</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Histórico/Pendências do Proponente</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
